--- a/output/stock_quant_scores/AMD_income_df.xlsx
+++ b/output/stock_quant_scores/AMD_income_df.xlsx
@@ -1341,7 +1341,9 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="n">
+        <v>3703000000</v>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -1352,13 +1354,17 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>2.61</v>
+      </c>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="n">
         <v>1000000</v>
       </c>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
+      <c r="Z6" t="n">
+        <v>3162000000</v>
+      </c>
       <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
@@ -1384,9 +1390,13 @@
       <c r="AU6" t="inlineStr"/>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
+      <c r="AX6" t="n">
+        <v>7929000000</v>
+      </c>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="n">
+        <v>16434000000</v>
+      </c>
       <c r="BA6" t="inlineStr"/>
     </row>
   </sheetData>
